--- a/Data/27/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -244,7 +244,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699387</t>
+    <t>10699518</t>
   </si>
   <si>
     <t>Passed</t>
@@ -256,10 +256,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>Margie</t>
-  </si>
-  <si>
-    <t>Schaefer</t>
+    <t>Virgil</t>
+  </si>
+  <si>
+    <t>Walker</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -397,22 +397,22 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699421</t>
+    <t>10699519</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>Michele</t>
-  </si>
-  <si>
-    <t>Hayes</t>
+    <t>Garnet</t>
+  </si>
+  <si>
+    <t>Kunde</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 91589263</t>
+    <t>Auto 96981989</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -1387,7 +1387,7 @@
         <v>104</v>
       </c>
       <c r="AT2" s="18">
-        <v>9461110784</v>
+        <v>9461110901</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>105</v>
@@ -1402,7 +1402,7 @@
         <v>107</v>
       </c>
       <c r="AY2" s="19">
-        <v>142743085</v>
+        <v>142743099</v>
       </c>
       <c r="AZ2" s="13" t="s">
         <v>105</v>
@@ -1631,7 +1631,7 @@
         <v>104</v>
       </c>
       <c r="AT3" s="18">
-        <v>9461110900</v>
+        <v>9461110902</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>105</v>
@@ -1646,7 +1646,7 @@
         <v>107</v>
       </c>
       <c r="AY3" s="19">
-        <v>152733090</v>
+        <v>152733400</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>105</v>

--- a/Data/27/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{CAFFCDDE-C4C9-448B-B813-A10E721B7068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="140">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -244,12 +259,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699518</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>895 Retail Team 1 (Sepap Pusube (10573442) (Inherited))</t>
   </si>
   <si>
@@ -395,9 +404,6 @@
   </si>
   <si>
     <t>Test2</t>
-  </si>
-  <si>
-    <t>10699519</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
@@ -448,54 +454,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
-      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -507,7 +513,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999816888943144"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -552,16 +558,28 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -906,10 +924,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CN17"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="109.7265625" style="1" customWidth="1"/>
@@ -990,10 +1008,11 @@
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
     <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
     <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
-    <col min="80" max="16384" width="8.90625" style="1" customWidth="1"/>
+    <col min="80" max="80" width="8.90625" style="1" customWidth="1"/>
+    <col min="81" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1245,45 +1264,41 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="H2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="K2" s="13">
         <v>45597</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N2" s="11">
         <v>1</v>
@@ -1292,72 +1307,72 @@
         <v>213111231</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="T2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="S2" s="12" t="s">
+      <c r="V2" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="W2" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X2" s="13">
         <f t="shared" ref="X2:X3" si="0">K2</f>
         <v>45597</v>
       </c>
       <c r="Y2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AB2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AC2" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AD2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AE2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AF2" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>98</v>
       </c>
       <c r="AG2" s="16">
         <v>20</v>
       </c>
       <c r="AH2" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AI2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK2" s="13">
+      <c r="AK2" s="13" t="str">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL2" s="13">
         <f t="shared" ref="AL2:AL3" si="2">K2</f>
@@ -1368,10 +1383,10 @@
         <v>45597</v>
       </c>
       <c r="AN2" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AP2" s="11">
         <v>100</v>
@@ -1381,79 +1396,79 @@
         <v>45687</v>
       </c>
       <c r="AR2" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AS2" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT2" s="18">
+        <v>9461110905</v>
+      </c>
+      <c r="AU2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="18">
-        <v>9461110901</v>
-      </c>
-      <c r="AU2" s="13" t="s">
+      <c r="AW2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX2" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="AV2" s="13" t="s">
+      <c r="AY2" s="19">
+        <v>152733405</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB2" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="AW2" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX2" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY2" s="19">
-        <v>142743099</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="BA2" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="BB2" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="BC2" s="13">
         <v>34284</v>
       </c>
       <c r="BD2" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="BE2" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF2" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="17" t="s">
+      <c r="BH2" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BI2" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BJ2" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BI2" s="8" t="s">
+      <c r="BK2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="BL2" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="17" t="s">
+      <c r="BM2" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BL2" s="14" t="s">
+      <c r="BN2" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="BM2" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="BN2" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="BO2" s="14">
         <v>2024</v>
       </c>
       <c r="BP2" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BQ2" s="14">
         <v>2021</v>
@@ -1462,72 +1477,68 @@
         <v>2024</v>
       </c>
       <c r="BS2" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="BT2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="BV2" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="14" t="s">
+      <c r="BW2" s="20" t="s">
         <v>120</v>
-      </c>
-      <c r="BU2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BV2" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW2" s="20" t="s">
-        <v>122</v>
       </c>
       <c r="BX2" s="20">
         <v>213</v>
       </c>
       <c r="BY2" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="BZ2" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="CA2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="BZ2" s="20" t="s">
+    </row>
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="20" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="E3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="G3" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="I3" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K3" s="13">
         <v>45597</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" s="11">
         <v>1</v>
@@ -1536,72 +1547,72 @@
         <v>213111231</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="T3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="U3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="S3" s="12" t="s">
+      <c r="V3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="T3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="W3" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X3" s="13">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z3" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA3" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="12" t="s">
+      <c r="AB3" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF3" s="8" t="s">
         <v>132</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>135</v>
       </c>
       <c r="AG3" s="16">
         <v>40</v>
       </c>
       <c r="AH3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ3" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AI3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ3" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK3" s="13">
+      <c r="AK3" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL3" s="13">
         <f t="shared" si="2"/>
@@ -1612,10 +1623,10 @@
         <v>45597</v>
       </c>
       <c r="AN3" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AP3" s="11">
         <v>100</v>
@@ -1625,79 +1636,79 @@
         <v>45687</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AS3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT3" s="18">
+        <v>9461110906</v>
+      </c>
+      <c r="AU3" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="18">
-        <v>9461110902</v>
-      </c>
-      <c r="AU3" s="13" t="s">
+      <c r="AW3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX3" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="AV3" s="13" t="s">
+      <c r="AY3" s="19">
+        <v>152733406</v>
+      </c>
+      <c r="AZ3" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA3" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB3" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="AW3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX3" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY3" s="19">
-        <v>152733400</v>
-      </c>
-      <c r="AZ3" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="BA3" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="BB3" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="BC3" s="13">
         <v>34284</v>
       </c>
       <c r="BD3" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="BE3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG3" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="17" t="s">
+      <c r="BH3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="BG3" s="11" t="s">
+      <c r="BI3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="11" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BI3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="BJ3" s="17" t="s">
-        <v>114</v>
-      </c>
       <c r="BK3" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BL3" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BM3" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BN3" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="BO3" s="14">
         <v>2000</v>
       </c>
       <c r="BP3" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BQ3" s="14">
         <v>1995</v>
@@ -1706,34 +1717,34 @@
         <v>2000</v>
       </c>
       <c r="BS3" s="14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="BT3" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="BU3" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BV3" s="20" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="BW3" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="BX3" s="20">
         <v>201</v>
       </c>
       <c r="BY3" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="BZ3" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="CA3" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="BZ3" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" s="20" t="s">
-        <v>125</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1814,7 +1825,7 @@
       <c r="BZ4" s="20"/>
       <c r="CA4" s="20"/>
     </row>
-    <row r="5" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1895,7 +1906,7 @@
       <c r="BZ5" s="20"/>
       <c r="CA5" s="20"/>
     </row>
-    <row r="6" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1976,7 +1987,7 @@
       <c r="BZ6" s="20"/>
       <c r="CA6" s="20"/>
     </row>
-    <row r="7" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="21"/>
       <c r="C7" s="8"/>
@@ -2057,7 +2068,7 @@
       <c r="BZ7" s="20"/>
       <c r="CA7" s="20"/>
     </row>
-    <row r="8" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="8"/>
@@ -2138,7 +2149,7 @@
       <c r="BZ8" s="20"/>
       <c r="CA8" s="20"/>
     </row>
-    <row r="9" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="21"/>
       <c r="C9" s="8"/>
@@ -2219,7 +2230,7 @@
       <c r="BZ9" s="20"/>
       <c r="CA9" s="20"/>
     </row>
-    <row r="10" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2300,7 +2311,7 @@
       <c r="BZ10" s="20"/>
       <c r="CA10" s="20"/>
     </row>
-    <row r="11" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2381,7 +2392,7 @@
       <c r="BZ11" s="20"/>
       <c r="CA11" s="20"/>
     </row>
-    <row r="12" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="21"/>
       <c r="C12" s="8"/>
@@ -2462,7 +2473,7 @@
       <c r="BZ12" s="20"/>
       <c r="CA12" s="20"/>
     </row>
-    <row r="13" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="21"/>
       <c r="C13" s="8"/>
@@ -2543,7 +2554,7 @@
       <c r="BZ13" s="20"/>
       <c r="CA13" s="20"/>
     </row>
-    <row r="14" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="21"/>
       <c r="C14" s="8"/>
@@ -2624,7 +2635,7 @@
       <c r="BZ14" s="20"/>
       <c r="CA14" s="20"/>
     </row>
-    <row r="15" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="8"/>
@@ -2705,7 +2716,7 @@
       <c r="BZ15" s="20"/>
       <c r="CA15" s="20"/>
     </row>
-    <row r="16" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="8"/>
@@ -2786,50 +2797,26 @@
       <c r="BZ16" s="20"/>
       <c r="CA16" s="20"/>
     </row>
-    <row r="17" ht="15.65" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="46:51" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AT17" s="19"/>
       <c r="AY17" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16 Y10:Y16 W10:W16 T10:T16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16 Y2:Y16 W2:W16 T2:T16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16 J10:J16" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>INDIRECT($D2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16 J2:J16" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J16">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J16">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10:W16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y10:Y16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y16">
-      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>